--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -289,7 +289,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t>Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,generacion oc fabricación externa 4388,Generacion Oc OT4080</t>
+    <t>Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,generacion oc fabricación externa 4388,Generacion Oc OT4080,Generacion Oc OT 4075 ,Generacion Oc OT 4413</t>
   </si>
   <si>
     <t>1217690801316042</t>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46255.651865231484</v>
+        <v>46261.171524317135</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>42</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46260.17248113426</v>
+        <v>46261.197462094904</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -1954,8 +1954,8 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>46</v>
+      <c r="T12" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U12" s="12" t="s">
         <v>47</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46255.651866562504</v>
+        <v>46261.1714268287</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46255.651865555556</v>
+        <v>46261.171429062495</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46258.603164988424</v>
+        <v>46261.60066953704</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46255.64947826389</v>
+        <v>46261.176095902774</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>164</v>
@@ -3853,8 +3853,8 @@
       <c r="S45" s="10">
         <v>0</v>
       </c>
-      <c r="T45" s="7" t="s">
-        <v>46</v>
+      <c r="T45" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="U45" s="11" t="s">
         <v>74</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46255.648011412035</v>
+        <v>46262.17376020833</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -151,22 +151,22 @@
     <t>Ingenieria Servicios:,propuesta tableros</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1217690801234161</t>
+  </si>
+  <si>
+    <t>Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1217690801234161</t>
-  </si>
-  <si>
-    <t>Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
   </si>
   <si>
     <t>1217653008288243</t>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46261.171524317135</v>
+        <v>46262.20306665509</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>42</v>
@@ -1781,16 +1781,16 @@
       <c r="S9" s="10">
         <v>0</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46254.64652826389</v>
@@ -1800,16 +1800,16 @@
         <v>46255.65186644676</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I10" s="5">
         <v>46328</v>
@@ -1845,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="T10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -1958,7 +1958,7 @@
         <v>32</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46261.1714268287</v>
+        <v>46262.20306663195</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2017,11 +2017,11 @@
       <c r="S13" s="10">
         <v>0</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="T13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46261.171429062495</v>
+        <v>46262.203067395836</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2127,11 +2127,11 @@
       <c r="S15" s="10">
         <v>0</v>
       </c>
-      <c r="T15" s="7" t="s">
+      <c r="T15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U17" s="11" t="s">
         <v>74</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U19" s="11" t="s">
         <v>74</v>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U20" s="11" t="s">
         <v>74</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U21" s="11" t="s">
         <v>74</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U22" s="11" t="s">
         <v>74</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>74</v>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U25" s="11" t="s">
         <v>74</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U26" s="11" t="s">
         <v>74</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U27" s="11" t="s">
         <v>74</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U31" s="11" t="s">
         <v>74</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U32" s="11" t="s">
         <v>74</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>74</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>74</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U37" s="11" t="s">
         <v>74</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U40" s="11" t="s">
         <v>74</v>
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>74</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U47" s="11" t="s">
         <v>74</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U48" s="11" t="s">
         <v>74</v>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U50" s="11" t="s">
         <v>74</v>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U51" s="11" t="s">
         <v>74</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>74</v>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>74</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>74</v>
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>74</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>74</v>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>74</v>
@@ -4704,10 +4704,10 @@
         <v>0</v>
       </c>
       <c r="T59" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="U59" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>74</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>74</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>74</v>
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>74</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>74</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>74</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>74</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>74</v>
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>74</v>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U73" s="11" t="s">
         <v>74</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U74" s="11" t="s">
         <v>74</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>74</v>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U76" s="11" t="s">
         <v>74</v>
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U77" s="11" t="s">
         <v>74</v>
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U78" s="11" t="s">
         <v>74</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46262.17376020833</v>
+        <v>46263.16763372685</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2237,8 +2237,8 @@
       <c r="S17" s="10">
         <v>0</v>
       </c>
-      <c r="T17" s="7" t="s">
-        <v>51</v>
+      <c r="T17" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U17" s="11" t="s">
         <v>74</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46258.193211307866</v>
+        <v>46265.17357490741</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46258.193210868056</v>
+        <v>46265.17364371528</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>218</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -247,274 +247,274 @@
     <t>Propuesta compras:,Generación OC Tableros 4388</t>
   </si>
   <si>
+    <t>1217690861771872</t>
+  </si>
+  <si>
+    <t>propuesta corte laser</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Check Planos 4388</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Corte laser 4388 ,Generación OC corte laser 4388</t>
+  </si>
+  <si>
+    <t>1217690801304114</t>
+  </si>
+  <si>
+    <t>propuesta corte plasma</t>
+  </si>
+  <si>
+    <t>Check Planos 4388</t>
+  </si>
+  <si>
+    <t>Generación  oc corte plasma  4388</t>
+  </si>
+  <si>
+    <t>1217690861779512</t>
+  </si>
+  <si>
+    <t>propuesta mecanizado</t>
+  </si>
+  <si>
+    <t>generación oc mecanizado 4388</t>
+  </si>
+  <si>
+    <t>1217690861779525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,generacion oc fabricación externa 4388,Generacion Oc OT4080,Generacion Oc OT 4075 ,Generacion Oc OT 4413</t>
+  </si>
+  <si>
+    <t>1217690801316042</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros 4388,Corte laser 4388 </t>
+  </si>
+  <si>
+    <t>1217690801316048</t>
+  </si>
+  <si>
+    <t>Tableros 4388</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero 4388,Generación OC Tableros 4388</t>
+  </si>
+  <si>
+    <t>1217691623114601</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros 4388</t>
+  </si>
+  <si>
+    <t>Tableros 4388,Fabricación Tablero 4388</t>
+  </si>
+  <si>
+    <t>1217691623114622</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero 4388</t>
+  </si>
+  <si>
+    <t>Tableros 4388,RECEPCION FABRICACIÓN EXTERNA 4388,Recepcion Tableros 4388</t>
+  </si>
+  <si>
+    <t>1217691240188787</t>
+  </si>
+  <si>
+    <t>Motor 4388</t>
+  </si>
+  <si>
+    <t>Generación oc Motor 4388,Fabricación motor 4388,Planos motor proveedor 4388</t>
+  </si>
+  <si>
+    <t>1217691240188800</t>
+  </si>
+  <si>
+    <t>Generación oc Motor 4388</t>
+  </si>
+  <si>
+    <t>Motor 4388,Fabricación motor 4388,Planos motor proveedor 4388</t>
+  </si>
+  <si>
+    <t>1217691240199202</t>
+  </si>
+  <si>
+    <t>Fabricación motor 4388</t>
+  </si>
+  <si>
+    <t>Recepcion Motor 4388,Motor 4388</t>
+  </si>
+  <si>
+    <t>1217691240199218</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor 4388</t>
+  </si>
+  <si>
+    <t>Planos Definitivos 4388,Motor 4388</t>
+  </si>
+  <si>
+    <t>1217690801331356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4388 </t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>propuesta corte laser,Generación OC corte laser 4388,Fabricacion  corte laser 4388</t>
+  </si>
+  <si>
+    <t>1217690801331379</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser 4388</t>
+  </si>
+  <si>
+    <t>Corte laser 4388 ,Fabricacion  corte laser 4388</t>
+  </si>
+  <si>
+    <t>1217691238162928</t>
+  </si>
+  <si>
+    <t>Fabricacion  corte laser 4388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4388 ,Recepcion corte laser 4388 </t>
+  </si>
+  <si>
+    <t>1217690861830323</t>
+  </si>
+  <si>
+    <t>Corte plasma 4388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc Corte Plasma ,Generacion Oc Corte Plasma ,Fabricación corte plasma 4388 </t>
+  </si>
+  <si>
+    <t>1217690861830346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma 4388 </t>
+  </si>
+  <si>
+    <t>1217691240231259</t>
+  </si>
+  <si>
+    <t>Corte plasma 4388,Recepcion corte plasma 4388</t>
+  </si>
+  <si>
+    <t>1217691240231275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado 4388 </t>
+  </si>
+  <si>
+    <t>generación oc mecanizado 4388,fabricacion mecanizado 4388</t>
+  </si>
+  <si>
+    <t>1217690861846034</t>
+  </si>
+  <si>
+    <t>Mecanizado 4388 ,fabricacion mecanizado 4388</t>
+  </si>
+  <si>
+    <t>1217690861846050</t>
+  </si>
+  <si>
+    <t>fabricacion mecanizado 4388</t>
+  </si>
+  <si>
+    <t>Mecanizado 4388 ,Recepción mecanizado 4388</t>
+  </si>
+  <si>
+    <t>1217691240241805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4388 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>fabricación material con proveedor externo 4388 ,generacion oc fabricación externa 4388</t>
+  </si>
+  <si>
+    <t>1217691240241818</t>
+  </si>
+  <si>
+    <t>generacion oc fabricación externa 4388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo 4388 ,Fabricación externa 4388 </t>
+  </si>
+  <si>
+    <t>1217691240241834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo 4388 </t>
+  </si>
+  <si>
+    <t>Fabricación externa 4388 ,CONTROL DE CALIDAD FABRICACIONE XTERNA  4388</t>
+  </si>
+  <si>
+    <t>1217691238190496</t>
+  </si>
+  <si>
+    <t>CONTROL DE CALIDAD FABRICACIONE XTERNA  4388</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1217691238209859</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Check Planos 4388,Check pruebas FAT  4388,Planos Definitivos 4388,Planos Preliminar 4388</t>
+  </si>
+  <si>
+    <t>1217691238209865</t>
+  </si>
+  <si>
+    <t>Planos Preliminar 4388</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos Definitivos 4388,Check Planos 4388,Ingenieria y diseño:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1217690861771872</t>
-  </si>
-  <si>
-    <t>propuesta corte laser</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Check Planos 4388</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Corte laser 4388 ,Generación OC corte laser 4388</t>
-  </si>
-  <si>
-    <t>1217690801304114</t>
-  </si>
-  <si>
-    <t>propuesta corte plasma</t>
-  </si>
-  <si>
-    <t>Check Planos 4388</t>
-  </si>
-  <si>
-    <t>Generación  oc corte plasma  4388</t>
-  </si>
-  <si>
-    <t>1217690861779512</t>
-  </si>
-  <si>
-    <t>propuesta mecanizado</t>
-  </si>
-  <si>
-    <t>generación oc mecanizado 4388</t>
-  </si>
-  <si>
-    <t>1217690861779525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,generacion oc fabricación externa 4388,Generacion Oc OT4080,Generacion Oc OT 4075 ,Generacion Oc OT 4413</t>
-  </si>
-  <si>
-    <t>1217690801316042</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros 4388,Corte laser 4388 </t>
-  </si>
-  <si>
-    <t>1217690801316048</t>
-  </si>
-  <si>
-    <t>Tableros 4388</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero 4388,Generación OC Tableros 4388</t>
-  </si>
-  <si>
-    <t>1217691623114601</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros 4388</t>
-  </si>
-  <si>
-    <t>Tableros 4388,Fabricación Tablero 4388</t>
-  </si>
-  <si>
-    <t>1217691623114622</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero 4388</t>
-  </si>
-  <si>
-    <t>Tableros 4388,RECEPCION FABRICACIÓN EXTERNA 4388,Recepcion Tableros 4388</t>
-  </si>
-  <si>
-    <t>1217691240188787</t>
-  </si>
-  <si>
-    <t>Motor 4388</t>
-  </si>
-  <si>
-    <t>Generación oc Motor 4388,Fabricación motor 4388,Planos motor proveedor 4388</t>
-  </si>
-  <si>
-    <t>1217691240188800</t>
-  </si>
-  <si>
-    <t>Generación oc Motor 4388</t>
-  </si>
-  <si>
-    <t>Motor 4388,Fabricación motor 4388,Planos motor proveedor 4388</t>
-  </si>
-  <si>
-    <t>1217691240199202</t>
-  </si>
-  <si>
-    <t>Fabricación motor 4388</t>
-  </si>
-  <si>
-    <t>Recepcion Motor 4388,Motor 4388</t>
-  </si>
-  <si>
-    <t>1217691240199218</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor 4388</t>
-  </si>
-  <si>
-    <t>Planos Definitivos 4388,Motor 4388</t>
-  </si>
-  <si>
-    <t>1217690801331356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4388 </t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>propuesta corte laser,Generación OC corte laser 4388,Fabricacion  corte laser 4388</t>
-  </si>
-  <si>
-    <t>1217690801331379</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser 4388</t>
-  </si>
-  <si>
-    <t>Corte laser 4388 ,Fabricacion  corte laser 4388</t>
-  </si>
-  <si>
-    <t>1217691238162928</t>
-  </si>
-  <si>
-    <t>Fabricacion  corte laser 4388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4388 ,Recepcion corte laser 4388 </t>
-  </si>
-  <si>
-    <t>1217690861830323</t>
-  </si>
-  <si>
-    <t>Corte plasma 4388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc Corte Plasma ,Generacion Oc Corte Plasma ,Fabricación corte plasma 4388 </t>
-  </si>
-  <si>
-    <t>1217690861830346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma 4388 </t>
-  </si>
-  <si>
-    <t>1217691240231259</t>
-  </si>
-  <si>
-    <t>Corte plasma 4388,Recepcion corte plasma 4388</t>
-  </si>
-  <si>
-    <t>1217691240231275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado 4388 </t>
-  </si>
-  <si>
-    <t>generación oc mecanizado 4388,fabricacion mecanizado 4388</t>
-  </si>
-  <si>
-    <t>1217690861846034</t>
-  </si>
-  <si>
-    <t>Mecanizado 4388 ,fabricacion mecanizado 4388</t>
-  </si>
-  <si>
-    <t>1217690861846050</t>
-  </si>
-  <si>
-    <t>fabricacion mecanizado 4388</t>
-  </si>
-  <si>
-    <t>Mecanizado 4388 ,Recepción mecanizado 4388</t>
-  </si>
-  <si>
-    <t>1217691240241805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4388 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>fabricación material con proveedor externo 4388 ,generacion oc fabricación externa 4388</t>
-  </si>
-  <si>
-    <t>1217691240241818</t>
-  </si>
-  <si>
-    <t>generacion oc fabricación externa 4388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo 4388 ,Fabricación externa 4388 </t>
-  </si>
-  <si>
-    <t>1217691240241834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo 4388 </t>
-  </si>
-  <si>
-    <t>Fabricación externa 4388 ,CONTROL DE CALIDAD FABRICACIONE XTERNA  4388</t>
-  </si>
-  <si>
-    <t>1217691238190496</t>
-  </si>
-  <si>
-    <t>CONTROL DE CALIDAD FABRICACIONE XTERNA  4388</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1217691238209859</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Check Planos 4388,Check pruebas FAT  4388,Planos Definitivos 4388,Planos Preliminar 4388</t>
-  </si>
-  <si>
-    <t>1217691238209865</t>
-  </si>
-  <si>
-    <t>Planos Preliminar 4388</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos Definitivos 4388,Check Planos 4388,Ingenieria y diseño:</t>
   </si>
   <si>
     <t>1217690861928988</t>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46265.17357490741</v>
+        <v>46266.17605711806</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2300,8 +2300,8 @@
       <c r="S18" s="6">
         <v>0</v>
       </c>
-      <c r="T18" s="12" t="s">
-        <v>78</v>
+      <c r="T18" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U18" s="11" t="s">
         <v>74</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="9">
         <v>46254.646577928244</v>
@@ -2319,7 +2319,7 @@
         <v>46255.648102384264</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2349,10 +2349,10 @@
         <v>69</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46293</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46254.646581678244</v>
@@ -2382,7 +2382,7 @@
         <v>46255.648098680555</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2412,10 +2412,10 @@
         <v>69</v>
       </c>
       <c r="O20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P20" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46293</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46254.64658453704</v>
@@ -2445,7 +2445,7 @@
         <v>46255.64809487268</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2475,10 +2475,10 @@
         <v>69</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46293</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46254.64658703704</v>
@@ -2508,7 +2508,7 @@
         <v>46261.60066953704</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2538,10 +2538,10 @@
         <v>69</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46293</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46254.646600520835</v>
@@ -2571,7 +2571,7 @@
         <v>46255.63153184028</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -2595,7 +2595,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46254.64660371528</v>
@@ -2618,16 +2618,16 @@
         <v>46255.6482277662</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46266</v>
@@ -2645,13 +2645,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="5">
         <v>46324</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46254.64660673611</v>
@@ -2681,16 +2681,16 @@
         <v>46255.64833429398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46266</v>
@@ -2708,13 +2708,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46254.64660969908</v>
@@ -2740,16 +2740,16 @@
         <v>46255.64833090278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46275</v>
@@ -2767,13 +2767,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="9">
         <v>46254.646613854165</v>
@@ -2799,16 +2799,16 @@
         <v>46255.64822379629</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46261</v>
@@ -2826,10 +2826,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46254.64661664352</v>
@@ -2862,16 +2862,16 @@
         <v>46255.64845569445</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46261</v>
@@ -2889,13 +2889,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9">
         <v>46254.64661905092</v>
@@ -2915,16 +2915,16 @@
         <v>46255.64845204861</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46272</v>
@@ -2942,13 +2942,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46254.64662153935</v>
@@ -2968,16 +2968,16 @@
         <v>46255.648448541666</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46272</v>
@@ -2995,13 +2995,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" s="9">
         <v>46254.646623900466</v>
@@ -3021,16 +3021,16 @@
         <v>46255.64856259259</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="I31" s="9">
         <v>46294</v>
@@ -3048,13 +3048,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="9">
         <v>46309</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46254.6466275</v>
@@ -3084,16 +3084,16 @@
         <v>46255.64865931713</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="I32" s="5">
         <v>46294</v>
@@ -3111,13 +3111,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46254.64662996528</v>
@@ -3143,16 +3143,16 @@
         <v>46255.648656053236</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="I33" s="9">
         <v>46301</v>
@@ -3170,13 +3170,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46254.646633136574</v>
@@ -3202,16 +3202,16 @@
         <v>46255.648558553235</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46294</v>
@@ -3229,10 +3229,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="9">
         <v>46254.64663752315</v>
@@ -3265,16 +3265,16 @@
         <v>46255.648779247684</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="I35" s="9">
         <v>46294</v>
@@ -3292,13 +3292,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46254.64663938657</v>
@@ -3318,16 +3318,16 @@
         <v>46255.64877497686</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="I36" s="5">
         <v>46303</v>
@@ -3345,13 +3345,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46254.646642141204</v>
@@ -3371,16 +3371,16 @@
         <v>46255.64855493055</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="I37" s="9">
         <v>46294</v>
@@ -3398,10 +3398,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -3424,7 +3424,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46254.64664486111</v>
@@ -3434,16 +3434,16 @@
         <v>46255.64908260417</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="I38" s="5">
         <v>46294</v>
@@ -3461,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="9">
         <v>46254.64664726851</v>
@@ -3487,16 +3487,16 @@
         <v>46255.64907900463</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="I39" s="9">
         <v>46301</v>
@@ -3514,13 +3514,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46254.64665070602</v>
@@ -3540,16 +3540,16 @@
         <v>46255.64937756944</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46294</v>
@@ -3567,10 +3567,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46254.646656909725</v>
@@ -3603,16 +3603,16 @@
         <v>46255.64921094908</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I41" s="9">
         <v>46294</v>
@@ -3630,13 +3630,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3646,7 +3646,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46254.64665930555</v>
@@ -3656,16 +3656,16 @@
         <v>46255.649206898146</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I42" s="5">
         <v>46303</v>
@@ -3683,13 +3683,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46254.64666165509</v>
@@ -3709,16 +3709,16 @@
         <v>46255.64931121528</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46332</v>
@@ -3736,10 +3736,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46254.64671832176</v>
@@ -3762,7 +3762,7 @@
         <v>46255.64334491898</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>25</v>
@@ -3786,7 +3786,7 @@
         <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46254.64672103009</v>
@@ -3809,16 +3809,16 @@
         <v>46261.176095902774</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="I45" s="9">
         <v>46262</v>
@@ -3836,13 +3836,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9">
         <v>46268</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="12" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="U45" s="11" t="s">
         <v>74</v>
@@ -3878,10 +3878,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46281</v>
@@ -3899,7 +3899,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>170</v>
@@ -3935,16 +3935,16 @@
         <v>46255.649470578704</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="I47" s="9">
         <v>46289</v>
@@ -3962,7 +3962,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>173</v>
@@ -4025,7 +4025,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>179</v>
@@ -4138,7 +4138,7 @@
         <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>188</v>
@@ -4177,10 +4177,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46314</v>
@@ -4264,7 +4264,7 @@
         <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>194</v>
@@ -4303,10 +4303,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46314</v>
@@ -4390,7 +4390,7 @@
         <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>199</v>
@@ -4429,10 +4429,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I55" s="9">
         <v>46314</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46265.17364371528</v>
+        <v>46266.17605825231</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>218</v>
@@ -4813,8 +4813,8 @@
       <c r="S61" s="10">
         <v>0</v>
       </c>
-      <c r="T61" s="12" t="s">
-        <v>78</v>
+      <c r="T61" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U61" s="11" t="s">
         <v>74</v>
@@ -4862,7 +4862,7 @@
         <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>182</v>
@@ -4925,7 +4925,7 @@
         <v>182</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>182</v>
@@ -4988,7 +4988,7 @@
         <v>182</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46261.176095902774</v>
+        <v>46268.1705025463</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>163</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="267">
   <si>
     <t xml:space="preserve">50001587 - usach </t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>Planos Definitivos 4388,Check Planos 4388,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217690861928988</t>
@@ -2859,7 +2856,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46255.64845569445</v>
+        <v>46269.17174230324</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3806,7 +3803,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46268.1705025463</v>
+        <v>46269.17639482639</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>163</v>
@@ -3853,8 +3850,8 @@
       <c r="S45" s="10">
         <v>0</v>
       </c>
-      <c r="T45" s="12" t="s">
-        <v>167</v>
+      <c r="T45" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U45" s="11" t="s">
         <v>74</v>
@@ -3862,7 +3859,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46254.64672483796</v>
@@ -3872,7 +3869,7 @@
         <v>46255.64947474537</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -3902,10 +3899,10 @@
         <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="Q46" s="5">
         <v>46288</v>
@@ -3925,7 +3922,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46254.64673040509</v>
@@ -3965,10 +3962,10 @@
         <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46289</v>
@@ -3988,7 +3985,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46254.64674159722</v>
@@ -3998,16 +3995,16 @@
         <v>46255.6495339699</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46339</v>
@@ -4028,10 +4025,10 @@
         <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46339</v>
@@ -4051,7 +4048,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46254.646754699075</v>
@@ -4061,7 +4058,7 @@
         <v>46255.636225775466</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4085,7 +4082,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4098,7 +4095,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46254.64675688658</v>
@@ -4108,16 +4105,16 @@
         <v>46255.649623310186</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46310</v>
@@ -4135,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46311</v>
@@ -4161,7 +4158,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46254.64676135417</v>
@@ -4171,7 +4168,7 @@
         <v>46255.649733136575</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4198,13 +4195,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="9">
         <v>46315</v>
@@ -4224,7 +4221,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46254.6467652662</v>
@@ -4234,16 +4231,16 @@
         <v>46255.64961998843</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46310</v>
@@ -4261,13 +4258,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46311</v>
@@ -4287,7 +4284,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46254.6467686574</v>
@@ -4297,7 +4294,7 @@
         <v>46255.64972939815</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4324,13 +4321,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="9">
         <v>46315</v>
@@ -4350,7 +4347,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46254.6467727662</v>
@@ -4360,16 +4357,16 @@
         <v>46255.649616435185</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46310</v>
@@ -4387,13 +4384,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q54" s="5">
         <v>46311</v>
@@ -4413,7 +4410,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46254.64677601852</v>
@@ -4423,7 +4420,7 @@
         <v>46255.64972537037</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4450,13 +4447,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="9">
         <v>46315</v>
@@ -4476,7 +4473,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46254.646778877315</v>
@@ -4486,7 +4483,7 @@
         <v>46255.63788684028</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4510,7 +4507,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4523,7 +4520,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46254.64678087963</v>
@@ -4533,16 +4530,16 @@
         <v>46255.64983976852</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="I57" s="9">
         <v>46316</v>
@@ -4560,13 +4557,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="Q57" s="9">
         <v>46318</v>
@@ -4586,7 +4583,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46254.64678571759</v>
@@ -4596,16 +4593,16 @@
         <v>46255.64983620371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="I58" s="5">
         <v>46321</v>
@@ -4623,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="5">
         <v>46325</v>
@@ -4649,7 +4646,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46254.6467994213</v>
@@ -4659,16 +4656,16 @@
         <v>46260.57751050926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="I59" s="9">
         <v>46328</v>
@@ -4686,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46328</v>
@@ -4712,7 +4709,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46254.646810833336</v>
@@ -4722,7 +4719,7 @@
         <v>46255.63928070602</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -4746,7 +4743,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -4759,7 +4756,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46254.64681284722</v>
@@ -4769,16 +4766,16 @@
         <v>46266.17605825231</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I61" s="9">
         <v>46262</v>
@@ -4796,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>63</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q61" s="9">
         <v>46265</v>
@@ -4822,7 +4819,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46254.646816990746</v>
@@ -4832,16 +4829,16 @@
         <v>46255.64996159722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46302</v>
@@ -4859,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q62" s="5">
         <v>46303</v>
@@ -4885,7 +4882,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46254.64682097222</v>
@@ -4895,16 +4892,16 @@
         <v>46255.64995738426</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I63" s="9">
         <v>46325</v>
@@ -4922,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q63" s="9">
         <v>46325</v>
@@ -4948,7 +4945,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46254.64692375</v>
@@ -4958,16 +4955,16 @@
         <v>46255.64995386574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I64" s="5">
         <v>46335</v>
@@ -4985,7 +4982,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>104</v>
@@ -5011,7 +5008,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="9">
         <v>46254.646927407404</v>
@@ -5021,7 +5018,7 @@
         <v>46255.64360596065</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5045,7 +5042,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5058,7 +5055,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46254.64693065972</v>
@@ -5068,7 +5065,7 @@
         <v>46255.65006753472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5095,13 +5092,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="5">
         <v>46335</v>
@@ -5121,7 +5118,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46254.646966782406</v>
@@ -5131,7 +5128,7 @@
         <v>46255.65006378472</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5158,13 +5155,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q67" s="9">
         <v>46336</v>
@@ -5184,7 +5181,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46254.6469462963</v>
@@ -5194,7 +5191,7 @@
         <v>46255.6500599537</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5219,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q68" s="5">
         <v>46337</v>
@@ -5245,7 +5242,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
         <v>46254.64699303241</v>
@@ -5255,7 +5252,7 @@
         <v>46255.65005642361</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5282,13 +5279,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q69" s="9">
         <v>46338</v>
@@ -5308,7 +5305,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46254.647011319445</v>
@@ -5318,7 +5315,7 @@
         <v>46255.65005247685</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5345,13 +5342,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="5">
         <v>46342</v>
@@ -5371,7 +5368,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B71" s="9">
         <v>46254.64706888889</v>
@@ -5381,7 +5378,7 @@
         <v>46255.644517175926</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5405,7 +5402,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5418,7 +5415,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46254.6470725463</v>
@@ -5428,16 +5425,16 @@
         <v>46255.65012431713</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5455,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q72" s="5">
         <v>46282</v>
@@ -5481,7 +5478,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B73" s="9">
         <v>46254.6471178125</v>
@@ -5491,7 +5488,7 @@
         <v>46255.65017988426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5518,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46344</v>
@@ -5544,7 +5541,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46254.64716206018</v>
@@ -5554,16 +5551,16 @@
         <v>46255.6502341088</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="I74" s="5">
         <v>46345</v>
@@ -5581,13 +5578,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q74" s="5">
         <v>46345</v>
@@ -5607,7 +5604,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B75" s="9">
         <v>46254.647253310184</v>
@@ -5617,16 +5614,16 @@
         <v>46255.65029092593</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="I75" s="9">
         <v>46346</v>
@@ -5644,13 +5641,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q75" s="9">
         <v>46346</v>
@@ -5670,7 +5667,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B76" s="5">
         <v>46254.64729115741</v>
@@ -5680,7 +5677,7 @@
         <v>46255.64545114583</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5704,7 +5701,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5723,7 +5720,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B77" s="9">
         <v>46254.64729417824</v>
@@ -5733,16 +5730,16 @@
         <v>46255.65036554398</v>
       </c>
       <c r="E77" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="10" t="s">
+      <c r="H77" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="I77" s="9">
         <v>46349</v>
@@ -5760,13 +5757,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q77" s="9">
         <v>46357</v>
@@ -5786,7 +5783,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B78" s="5">
         <v>46254.64729771991</v>
@@ -5796,16 +5793,16 @@
         <v>46255.65036190972</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46349</v>
@@ -5823,13 +5820,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="5">
         <v>46357</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -2675,7 +2675,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46255.64833429398</v>
+        <v>46274.16994162037</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="268">
   <si>
     <t xml:space="preserve">50001587 - usach </t>
   </si>
@@ -758,6 +758,9 @@
   </si>
   <si>
     <t>Logistica:,Embalaje 4388</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217691240750948</t>
@@ -5422,7 +5425,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46255.65012431713</v>
+        <v>46275.14170949074</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>245</v>
@@ -5469,8 +5472,8 @@
       <c r="S72" s="6">
         <v>0</v>
       </c>
-      <c r="T72" s="7" t="s">
-        <v>51</v>
+      <c r="T72" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>74</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46254.6471178125</v>
@@ -5488,7 +5491,7 @@
         <v>46255.65017988426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5521,7 +5524,7 @@
         <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46344</v>
@@ -5541,7 +5544,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46254.64716206018</v>
@@ -5551,7 +5554,7 @@
         <v>46255.6502341088</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5581,10 +5584,10 @@
         <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q74" s="5">
         <v>46345</v>
@@ -5604,7 +5607,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B75" s="9">
         <v>46254.647253310184</v>
@@ -5614,7 +5617,7 @@
         <v>46255.65029092593</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5644,10 +5647,10 @@
         <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q75" s="9">
         <v>46346</v>
@@ -5667,7 +5670,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B76" s="5">
         <v>46254.64729115741</v>
@@ -5677,7 +5680,7 @@
         <v>46255.64545114583</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5701,7 +5704,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5720,7 +5723,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B77" s="9">
         <v>46254.64729417824</v>
@@ -5730,16 +5733,16 @@
         <v>46255.65036554398</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I77" s="9">
         <v>46349</v>
@@ -5757,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q77" s="9">
         <v>46357</v>
@@ -5783,7 +5786,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46254.64729771991</v>
@@ -5793,16 +5796,16 @@
         <v>46255.65036190972</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46349</v>
@@ -5820,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q78" s="5">
         <v>46357</v>
